--- a/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T05:20:25+00:00</t>
+    <t>2026-09-28T10:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:16:57+00:00</t>
+    <t>2026-09-28T10:26:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
+++ b/1.0.0-ballot/StructureDefinition-onko-condition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T10:26:56+00:00</t>
+    <t>2026-09-28T11:29:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
